--- a/output/Bracket_2923090749942157798.xlsx
+++ b/output/Bracket_2923090749942157798.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amgal\Documents\Data Science\KingfisherCourt\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7AF1B45-E03A-4272-8ABE-EB28E4554C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0A77363-D6F8-404C-AB44-11A628FB19D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
